--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_o_higgins.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:51</t>
+    <t xml:space="preserve">2026-09-24 00:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -822,16 +822,16 @@
         <v>0.19</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="15">
@@ -842,19 +842,19 @@
         <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.57</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>-0.05</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="16">
@@ -868,13 +868,13 @@
         <v>0.45</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.2</v>
@@ -888,19 +888,19 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_o_higgins.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:42</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_o_higgins.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
